--- a/artfynd/A 8610-2026 artfynd.xlsx
+++ b/artfynd/A 8610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133996972</v>
+        <v>131651216</v>
       </c>
       <c r="B2" t="n">
-        <v>58410</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bye Öst, Bye Öst, Jmt</t>
+          <t>Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493057</v>
+        <v>493082</v>
       </c>
       <c r="R2" t="n">
-        <v>7016921</v>
+        <v>7016901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:56</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:56</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133997026</v>
+        <v>133997101</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,56 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bye Öst, Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493039</v>
+        <v>493105</v>
       </c>
       <c r="R3" t="n">
-        <v>7016915</v>
+        <v>7016875</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1059,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133997588</v>
+        <v>133996972</v>
       </c>
       <c r="B5" t="n">
         <v>58410</v>
@@ -1087,11 +1053,7 @@
           <t>Linnaeus, 1766</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>hane</t>
@@ -1102,24 +1064,19 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bye Öst, Bye Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493155</v>
+        <v>493057</v>
       </c>
       <c r="R5" t="n">
-        <v>7016795</v>
+        <v>7016921</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,6 +1144,516 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133997588</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bye Öst, Bye Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493155</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7016795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133997026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bye Öst, Bye Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7016915</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133997657</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bye Öst, Bye Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493140</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7016812</v>
+      </c>
+      <c r="S8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133996950</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bye Öst, Bye Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493053</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7016916</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8610-2026 artfynd.xlsx
+++ b/artfynd/A 8610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131651216</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133996972</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1406,6 +1436,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1537,6 +1572,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997657</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1654,8 +1694,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133996950</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>